--- a/out/Attention-mamba2_repeat_4_000005.xlsx
+++ b/out/Attention-mamba2_repeat_4_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.82870570880941</v>
+        <v>3.491217805496785</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.216984246204107</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-3.82870570880941</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.216984246204107</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.216984246204107</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2554444171274072</v>
+        <v>4.091217805496784</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2554444171274072</v>
+        <v>3.491217805496785</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.816984246204107</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2554444171274072</v>
+        <v>3.491217805496785</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2554444171274072</v>
+        <v>3.491217805496785</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_4_000005.xlsx
+++ b/out/Attention-mamba2_repeat_4_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-3.82870570880941</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-3.82870570880941</v>
+        <v>-1.326163885826609</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.3926438570410504</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445078</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_4_000005.xlsx
+++ b/out/Attention-mamba2_repeat_4_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1931170970201492</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1217991560697556</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1440746039152145</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.127107098698616</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1234923303127289</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1256914138793945</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1375213116407394</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.1233651041984558</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.09381736814975739</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.100152313709259</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.09333004057407379</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.09034661203622818</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.08201932907104492</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.09241648018360138</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.09817446768283844</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.1281710118055344</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.459683914612167</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.1219141781330109</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.326163885826609</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.05116852000355721</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3926438570410504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01278674229979515</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.04478224739432335</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0237811841070652</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.02394301071763039</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.004857391119003296</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.04174279049038887</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.007014039903879166</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01725228503346443</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.03642875328660011</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.009945955127477646</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01843457296490669</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.04509701952338219</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.07902534306049347</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.02024313434958458</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.06723169982433319</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01774026826024055</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01768771186470985</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0667663961648941</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.004136413335800171</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01276515051722527</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01896379142999649</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01532040163874626</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02241618558764458</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01120985671877861</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01733724400401115</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02013074234127998</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01259714737534523</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01617038622498512</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01716507598757744</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01233776286244392</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01542473211884499</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01063395664095879</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01730196550488472</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01268903911113739</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01600023731589317</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02125615999102592</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.16</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.02075702324509621</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.08262914419174194</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01674225926399231</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.02777793630957603</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.02264551445841789</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01392457261681557</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.03261373937129974</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.006728727370500565</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01857123896479607</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01874103769659996</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0197717659175396</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.02172182872891426</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01793060824275017</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01823655888438225</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01677140220999718</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.0124533586204052</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.007863979786634445</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.04249730333685875</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.09184549748897552</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.07392393052577972</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.07210193574428558</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.06924441456794739</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0878216028213501</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.07279287278652191</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0690758228302002</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.06470127403736115</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.08047237992286682</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.108867809176445</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05044155940413475</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.08800765872001648</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.06544382870197296</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0459279976785183</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.1033267080783844</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.08389414846897125</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.08474476635456085</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.04702375456690788</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06539112329483032</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.05029744282364845</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04187889024615288</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0674336701631546</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.08934587240219116</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.06550268828868866</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.06102704629302025</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.06295125186443329</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0358247421681881</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.06407810747623444</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.09097114205360413</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.06757120788097382</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.06286095082759857</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.08452141284942627</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.1011532098054886</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.04877655580639839</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.08996924757957458</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.05252351984381676</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.06142759695649147</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03171908482909203</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03959660604596138</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.06049570813775063</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.1294657737016678</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.08091659843921661</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.1227875947952271</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.104094073176384</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.1021129488945007</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.1269252598285675</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.03917663171887398</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3408761717445078</v>
+        <v>0.3</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0577603243291378</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.1241020411252975</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.09135837852954865</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.08098945021629333</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.05977204814553261</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3408761717445078</v>
+        <v>-0.7900000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.06381556391716003</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3408761717445078</v>
+        <v>-1.14</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_4_000005.xlsx
+++ b/out/Attention-mamba2_repeat_4_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1931170970201492</v>
+        <v>-0.1900047957897186</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1217991560697556</v>
+        <v>-0.1188628673553467</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1440746039152145</v>
+        <v>-0.1406626552343369</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.127107098698616</v>
+        <v>-0.1234805956482887</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1234923303127289</v>
+        <v>-0.1195866018533707</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1256914138793945</v>
+        <v>-0.121678851544857</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1375213116407394</v>
+        <v>-0.1333531886339188</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.1233651041984558</v>
+        <v>-0.1188858225941658</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.09381736814975739</v>
+        <v>-0.08948732912540436</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.100152313709259</v>
+        <v>-0.09561095386743546</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.09333004057407379</v>
+        <v>-0.08898325264453888</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.09034661203622818</v>
+        <v>-0.08590810000896454</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.08201932907104492</v>
+        <v>-0.07781855762004852</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.09241648018360138</v>
+        <v>-0.08810190111398697</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.09817446768283844</v>
+        <v>-0.09437946230173111</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.1281710118055344</v>
+        <v>-0.1245811656117439</v>
       </c>
       <c r="JB17" t="n">
         <v>0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.1219141781330109</v>
+        <v>-0.1192479953169823</v>
       </c>
       <c r="JB18" t="n">
         <v>0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.05116852000355721</v>
+        <v>0.05048494040966034</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.01278674229979515</v>
+        <v>0.0121745765209198</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.04478224739432335</v>
+        <v>0.04359238594770432</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.0237811841070652</v>
+        <v>0.0228709951043129</v>
       </c>
       <c r="JB22" t="n">
         <v>0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.02394301071763039</v>
+        <v>0.02332195639610291</v>
       </c>
       <c r="JB23" t="n">
         <v>0.8599999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.004857391119003296</v>
+        <v>0.004085812717676163</v>
       </c>
       <c r="JB24" t="n">
         <v>0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.04174279049038887</v>
+        <v>0.04125151038169861</v>
       </c>
       <c r="JB25" t="n">
         <v>0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.007014039903879166</v>
+        <v>0.006369572132825851</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.01725228503346443</v>
+        <v>0.01674103364348412</v>
       </c>
       <c r="JB27" t="n">
         <v>0.1199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.03642875328660011</v>
+        <v>0.03584271669387817</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.009945955127477646</v>
+        <v>0.009356383234262466</v>
       </c>
       <c r="JB29" t="n">
         <v>0.1199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.01843457296490669</v>
+        <v>0.01794564351439476</v>
       </c>
       <c r="JB30" t="n">
         <v>0.2599999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.04509701952338219</v>
+        <v>0.04432575404644012</v>
       </c>
       <c r="JB31" t="n">
         <v>0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.07902534306049347</v>
+        <v>0.07770692557096481</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.02024313434958458</v>
+        <v>0.01940133422613144</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.06723169982433319</v>
+        <v>0.06643323600292206</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.01774026826024055</v>
+        <v>0.01637226343154907</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.01768771186470985</v>
+        <v>0.01640588045120239</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.16</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0667663961648941</v>
+        <v>0.06560598313808441</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.004136413335800171</v>
+        <v>0.00271281972527504</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.01276515051722527</v>
+        <v>0.01136688888072968</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.01896379142999649</v>
+        <v>0.01751589775085449</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.01532040163874626</v>
+        <v>0.01380600407719612</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.02000000000000007</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.02241618558764458</v>
+        <v>0.02088908851146698</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.01120985671877861</v>
+        <v>0.009965505450963974</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01733724400401115</v>
+        <v>0.01618460565805435</v>
       </c>
       <c r="JB44" t="n">
         <v>0.5799999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.02013074234127998</v>
+        <v>0.01876083016395569</v>
       </c>
       <c r="JB45" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01259714737534523</v>
+        <v>0.01131728291511536</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01617038622498512</v>
+        <v>0.01487315073609352</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01716507598757744</v>
+        <v>0.01576370000839233</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.01233776286244392</v>
+        <v>0.01103077828884125</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01542473211884499</v>
+        <v>0.01402066648006439</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.01063395664095879</v>
+        <v>0.009278368204832077</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.01730196550488472</v>
+        <v>0.01585743576288223</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.01268903911113739</v>
+        <v>0.01130063831806183</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.8599999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.01600023731589317</v>
+        <v>0.01467376947402954</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.02125615999102592</v>
+        <v>0.01979771628975868</v>
       </c>
       <c r="JB55" t="n">
         <v>0.16</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.02075702324509621</v>
+        <v>0.01949003338813782</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.08262914419174194</v>
+        <v>0.0816887691617012</v>
       </c>
       <c r="JB57" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.01674225926399231</v>
+        <v>0.01516688242554665</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.02777793630957603</v>
+        <v>0.02630462497472763</v>
       </c>
       <c r="JB59" t="n">
         <v>0.16</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.02264551445841789</v>
+        <v>0.02108629047870636</v>
       </c>
       <c r="JB60" t="n">
         <v>0.02000000000000007</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.01392457261681557</v>
+        <v>0.01249039173126221</v>
       </c>
       <c r="JB61" t="n">
         <v>0.02000000000000007</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.03261373937129974</v>
+        <v>0.0311446450650692</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.5799999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.006728727370500565</v>
+        <v>0.005625251680612564</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.01857123896479607</v>
+        <v>0.01741331815719604</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.01874103769659996</v>
+        <v>0.01767681166529655</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.0197717659175396</v>
+        <v>0.01876302808523178</v>
       </c>
       <c r="JB66" t="n">
         <v>0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.02172182872891426</v>
+        <v>0.02052540332078934</v>
       </c>
       <c r="JB67" t="n">
         <v>0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01793060824275017</v>
+        <v>0.01678856462240219</v>
       </c>
       <c r="JB68" t="n">
         <v>0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.01823655888438225</v>
+        <v>0.01711701974272728</v>
       </c>
       <c r="JB69" t="n">
         <v>0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.01677140220999718</v>
+        <v>0.01548480242490768</v>
       </c>
       <c r="JB70" t="n">
         <v>0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.0124533586204052</v>
+        <v>0.01112033799290657</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.4399999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.007863979786634445</v>
+        <v>0.006662432104349136</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.3</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.04249730333685875</v>
+        <v>0.04159659892320633</v>
       </c>
       <c r="JB73" t="n">
         <v>0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.09184549748897552</v>
+        <v>0.09114307165145874</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.07392393052577972</v>
+        <v>0.07338574528694153</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.07210193574428558</v>
+        <v>0.07116403430700302</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.06924441456794739</v>
+        <v>0.06851695477962494</v>
       </c>
       <c r="JB77" t="n">
         <v>0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.0878216028213501</v>
+        <v>0.08713889867067337</v>
       </c>
       <c r="JB78" t="n">
         <v>0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.07279287278652191</v>
+        <v>0.07175008207559586</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.0690758228302002</v>
+        <v>0.06796378642320633</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.06470127403736115</v>
+        <v>0.06367387622594833</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.08047237992286682</v>
+        <v>0.07981324940919876</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.108867809176445</v>
+        <v>0.1081680878996849</v>
       </c>
       <c r="JB83" t="n">
         <v>0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.05044155940413475</v>
+        <v>0.04912766814231873</v>
       </c>
       <c r="JB84" t="n">
         <v>0.2599999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.08800765872001648</v>
+        <v>0.08721369504928589</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.06544382870197296</v>
+        <v>0.06401866674423218</v>
       </c>
       <c r="JB86" t="n">
         <v>0.5799999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0459279976785183</v>
+        <v>0.04494934529066086</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.1033267080783844</v>
+        <v>0.1027990654110909</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.02000000000000007</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.08389414846897125</v>
+        <v>0.08319539576768875</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.08474476635456085</v>
+        <v>0.0837353840470314</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.04702375456690788</v>
+        <v>0.04564429819583893</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06539112329483032</v>
+        <v>0.06427710503339767</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.05029744282364845</v>
+        <v>0.04884663224220276</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.04187889024615288</v>
+        <v>0.04050970822572708</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.3</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.0674336701631546</v>
+        <v>0.06658767908811569</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.08934587240219116</v>
+        <v>0.08852047473192215</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.06550268828868866</v>
+        <v>0.06423638761043549</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.06102704629302025</v>
+        <v>0.05980487912893295</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.06295125186443329</v>
+        <v>0.0616181418299675</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0358247421681881</v>
+        <v>0.03433118015527725</v>
       </c>
       <c r="JB100" t="n">
         <v>0.3</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.06407810747623444</v>
+        <v>0.06320629268884659</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.09097114205360413</v>
+        <v>0.09016084671020508</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.06757120788097382</v>
+        <v>0.0663008838891983</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.06286095082759857</v>
+        <v>0.06177268177270889</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.08452141284942627</v>
+        <v>0.083820641040802</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1011532098054886</v>
+        <v>0.1002568230032921</v>
       </c>
       <c r="JB106" t="n">
         <v>0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.04877655580639839</v>
+        <v>0.0473909005522728</v>
       </c>
       <c r="JB107" t="n">
         <v>0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.08996924757957458</v>
+        <v>0.08904951065778732</v>
       </c>
       <c r="JB108" t="n">
         <v>0.1600000000000001</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.05252351984381676</v>
+        <v>0.05097859352827072</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.06142759695649147</v>
+        <v>0.05991286784410477</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.03171908482909203</v>
+        <v>0.03003470599651337</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.03959660604596138</v>
+        <v>0.03796316683292389</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.06049570813775063</v>
+        <v>0.05943506956100464</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.4399999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.1294657737016678</v>
+        <v>0.1287574172019958</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.08091659843921661</v>
+        <v>0.08014339953660965</v>
       </c>
       <c r="JB115" t="n">
         <v>0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.1227875947952271</v>
+        <v>0.1219172701239586</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.104094073176384</v>
+        <v>0.1033535823225975</v>
       </c>
       <c r="JB117" t="n">
         <v>0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.1021129488945007</v>
+        <v>0.101268045604229</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.1269252598285675</v>
+        <v>0.1259464919567108</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.03917663171887398</v>
+        <v>0.03746762871742249</v>
       </c>
       <c r="JB120" t="n">
         <v>0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.0577603243291378</v>
+        <v>0.0566680058836937</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.1241020411252975</v>
+        <v>0.1232940480113029</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.09135837852954865</v>
+        <v>0.09057395160198212</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.08098945021629333</v>
+        <v>0.08003050088882446</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.05977204814553261</v>
+        <v>0.05850578844547272</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.7900000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.06381556391716003</v>
+        <v>0.06267754733562469</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.14</v>
